--- a/E-Commerce/E-Commerce_Platform.xlsx
+++ b/E-Commerce/E-Commerce_Platform.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Testing\E-Commerce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98CF78F9-A5DF-45FD-8A61-F967925576AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ADAA7A4-16BF-4FE1-88C3-4D86C6A81B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="107">
   <si>
     <t>Test case ID</t>
   </si>
@@ -281,6 +281,141 @@
   </si>
   <si>
     <t xml:space="preserve">User successfully sorted the product details from A to Z </t>
+  </si>
+  <si>
+    <t>TC_009</t>
+  </si>
+  <si>
+    <t>Sort product by price from low to high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User can display product details in the dashboard and sort it based on price from low to high </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- open https://www.saucedemo.com/
+2- login with valid credentials.
+3- dashboard will display product inventory details.
+4- click on sort list and choose Price (low to high)
+</t>
+  </si>
+  <si>
+    <t>A user should be able to see the products sorted by price from low to high</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User successfully sorted the product details by price </t>
+  </si>
+  <si>
+    <t>TC_010</t>
+  </si>
+  <si>
+    <t>Sort product from  Z to A</t>
+  </si>
+  <si>
+    <t>User can display product details in the dashboard and sort it from Z to A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- open https://www.saucedemo.com/
+2- login with valid credentials.
+3- dashboard will display product inventory details.
+4- click on sort list and choose Name(Z to A)
+</t>
+  </si>
+  <si>
+    <t>A user should be able to see the products sorted from Z to A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User successfully sorted the product details from Z to A </t>
+  </si>
+  <si>
+    <t>TC_011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sort product by price from high to low </t>
+  </si>
+  <si>
+    <t>User can display product details in the dashboard and sort it based on price from high to low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- open https://www.saucedemo.com/
+2- login with valid credentials.
+3- dashboard will display product inventory details.
+4- click on sort list and choose Price (high to low)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A user should be able to see the products sorted by price from high to low </t>
+  </si>
+  <si>
+    <t>TC_012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add single product to the card </t>
+  </si>
+  <si>
+    <t xml:space="preserve">User can add a single product to the card for shopping </t>
+  </si>
+  <si>
+    <t>1- Open https://www.saucedemo.com/
+2- login with valid credentials.
+3- In dashboard, choose one product and click add to card button.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An add to card button changed to remove, and number 1 is showed in the shopping car </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Product is added to the card, text changed to remove and shopping car have one and it is also showed in visuals </t>
+  </si>
+  <si>
+    <t>TC_013</t>
+  </si>
+  <si>
+    <t>Add multiple products to the card</t>
+  </si>
+  <si>
+    <t>User can add multiple products to the card for shopping</t>
+  </si>
+  <si>
+    <t>1- Open https://www.saucedemo.com/
+2- login with valid credentials.
+3- In dashboard, for (Sauce Labs Backpack) click add to card.
+4- for (Sauce Labs Bike Light) click add to card.
+5- for (Sauce Labs Onesie) click add to card.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">card badge showed 3,
+Each product button changed to remove, and all products choosen added to the card, and the card button increased each time you add to the card </t>
+  </si>
+  <si>
+    <t>Prodcuts added to the card,text changed to remove in all product choosen and the shopping car increased.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove product from card </t>
+  </si>
+  <si>
+    <t>TC_014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User can remove product from the card </t>
+  </si>
+  <si>
+    <t>Product exists in the card</t>
+  </si>
+  <si>
+    <t>Product removed from the card,card badge decreased by one and shopping card prices updated automatically.</t>
+  </si>
+  <si>
+    <t>Card bagde should decreade by 1,
+and button text should change back to add to card, product should remove from the shopping card 
+and price should update automatically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- click on the shopping card 
+2- Click on remove (sauce Labs Backpack) product from the card.
+3- Click on remove (Sauce Labs Bike Light) product from the card.
+</t>
+  </si>
+  <si>
+    <t>TC_015</t>
   </si>
 </sst>
 </file>
@@ -353,7 +488,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -366,12 +501,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -457,7 +586,447 @@
                   <a14:compatExt spid="_x0000_s2055"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5C935AC-ED45-47A3-17FD-889979F31BF5}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>215900</xdr:colOff>
+          <xdr:row>8</xdr:row>
+          <xdr:rowOff>304800</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>692150</xdr:colOff>
+          <xdr:row>8</xdr:row>
+          <xdr:rowOff>768350</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2057" name="Object 9" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2057"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>209550</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>457200</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>730250</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>933450</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2058" name="Object 10" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2058"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>260350</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>762000</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>850900</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2059" name="Object 11" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2059"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000B080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>215900</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>298450</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>774700</xdr:colOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>812800</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2060" name="Object 12" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2060"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000C080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>114300</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>279400</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>723900</xdr:colOff>
+          <xdr:row>4</xdr:row>
+          <xdr:rowOff>781050</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2061" name="Object 13" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2061"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000D080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>171450</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>533400</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>711200</xdr:colOff>
+          <xdr:row>6</xdr:row>
+          <xdr:rowOff>1155700</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2062" name="Object 14" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2062"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000E080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>120650</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>311150</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>704850</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>901700</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2063" name="Object 15" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2063"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000F080000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>228600</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>546100</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>11</xdr:col>
+          <xdr:colOff>730250</xdr:colOff>
+          <xdr:row>9</xdr:row>
+          <xdr:rowOff>1085850</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="2065" name="Object 17" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s2065"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F158B9F4-5F43-154A-00AC-FADBA0E6A257}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -507,25 +1076,25 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>215900</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>304800</xdr:rowOff>
+          <xdr:colOff>133350</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>425450</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>692150</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>768350</xdr:rowOff>
+          <xdr:colOff>736600</xdr:colOff>
+          <xdr:row>10</xdr:row>
+          <xdr:rowOff>1047750</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2057" name="Object 9" hidden="1">
+            <xdr:cNvPr id="2067" name="Object 19" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2057"/>
+                  <a14:compatExt spid="_x0000_s2067"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{967CC5C0-5B30-04A2-8548-505811684064}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4B10B94-324E-2FF1-2FA7-8F5757686082}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -575,25 +1144,25 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>209550</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>457200</xdr:rowOff>
+          <xdr:colOff>184150</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>349250</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>730250</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>933450</xdr:rowOff>
+          <xdr:colOff>698500</xdr:colOff>
+          <xdr:row>11</xdr:row>
+          <xdr:rowOff>971550</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2058" name="Object 10" hidden="1">
+            <xdr:cNvPr id="2070" name="Object 22" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2058"/>
+                  <a14:compatExt spid="_x0000_s2070"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E212DA5F-B611-4EEC-94C2-743FB387FD2E}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03183288-B60B-70E7-6FEE-9E0E9934E526}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -643,25 +1212,25 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>184150</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>260350</xdr:rowOff>
+          <xdr:colOff>107950</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>628650</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>762000</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>850900</xdr:rowOff>
+          <xdr:colOff>723900</xdr:colOff>
+          <xdr:row>12</xdr:row>
+          <xdr:rowOff>1314450</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2059" name="Object 11" hidden="1">
+            <xdr:cNvPr id="2073" name="Object 25" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2059"/>
+                  <a14:compatExt spid="_x0000_s2073"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{41248991-A3FA-E15E-E5F1-B1693101497D}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DBED073-5186-2E63-E504-460AA399CCA2}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -711,25 +1280,25 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>215900</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>298450</xdr:rowOff>
+          <xdr:colOff>190500</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>285750</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>774700</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>812800</xdr:rowOff>
+          <xdr:colOff>717550</xdr:colOff>
+          <xdr:row>13</xdr:row>
+          <xdr:rowOff>863600</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2060" name="Object 12" hidden="1">
+            <xdr:cNvPr id="2076" name="Object 28" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2060"/>
+                  <a14:compatExt spid="_x0000_s2076"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF304587-DBB3-5968-A5EC-BA76A27AACDE}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A6BFE2F-E787-1EFF-A4CE-49164ED8ECE2}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -779,161 +1348,25 @@
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>114300</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>279400</xdr:rowOff>
+          <xdr:colOff>88900</xdr:colOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>508000</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>11</xdr:col>
-          <xdr:colOff>723900</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>781050</xdr:rowOff>
+          <xdr:colOff>679450</xdr:colOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>1193800</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
-            <xdr:cNvPr id="2061" name="Object 13" hidden="1">
+            <xdr:cNvPr id="2079" name="Object 31" hidden="1">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2061"/>
+                  <a14:compatExt spid="_x0000_s2079"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5992BD62-05E4-771E-914C-511594CBDD23}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd type="none" w="med" len="med"/>
-            </a:ln>
-            <a:effectLst/>
-            <a:extLst>
-              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                <a14:hiddenEffects>
-                  <a:effectLst>
-                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                      <a:srgbClr val="808080"/>
-                    </a:outerShdw>
-                  </a:effectLst>
-                </a14:hiddenEffects>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>11</xdr:col>
-          <xdr:colOff>171450</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>533400</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>11</xdr:col>
-          <xdr:colOff>711200</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>1155700</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2062" name="Object 14" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2062"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1B01FAC4-0B8C-72B8-0DAD-2D627B66981F}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off x="0" y="0"/>
-              <a:ext cx="0" cy="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd type="none" w="med" len="med"/>
-            </a:ln>
-            <a:effectLst/>
-            <a:extLst>
-              <a:ext uri="{AF507438-7753-43E0-B8FC-AC1667EBCBE1}">
-                <a14:hiddenEffects>
-                  <a:effectLst>
-                    <a:outerShdw dist="35921" dir="2700000" algn="ctr" rotWithShape="0">
-                      <a:srgbClr val="808080"/>
-                    </a:outerShdw>
-                  </a:effectLst>
-                </a14:hiddenEffects>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-        </xdr:sp>
-        <xdr:clientData/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>11</xdr:col>
-          <xdr:colOff>120650</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>311150</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>11</xdr:col>
-          <xdr:colOff>704850</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>901700</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="2063" name="Object 15" hidden="1">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s2063"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1DCCBE5-F226-3E3B-98B3-4F23F40395E6}"/>
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F4AD0AD3-41F2-5244-8751-8B6AB4D7065B}"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPr>
@@ -1183,7 +1616,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B189C1C1-9B4A-4367-9125-6615924950A8}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.7265625" customWidth="1"/>
@@ -1192,8 +1625,8 @@
     <col min="4" max="4" width="11.453125" customWidth="1"/>
     <col min="5" max="5" width="25.453125" customWidth="1"/>
     <col min="6" max="6" width="15.6328125" customWidth="1"/>
-    <col min="7" max="7" width="12.26953125" customWidth="1"/>
-    <col min="8" max="8" width="9.36328125" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="13.36328125" customWidth="1"/>
     <col min="12" max="12" width="12.36328125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1236,7 +1669,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="100" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B2" s="4" t="s">
@@ -1272,7 +1705,7 @@
       <c r="L2" s="4"/>
     </row>
     <row r="3" spans="1:12" ht="100" x14ac:dyDescent="0.25">
-      <c r="A3" s="8"/>
+      <c r="A3" s="6"/>
       <c r="B3" s="4" t="s">
         <v>30</v>
       </c>
@@ -1306,7 +1739,7 @@
       <c r="L3" s="4"/>
     </row>
     <row r="4" spans="1:12" ht="100" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
+      <c r="A4" s="6"/>
       <c r="B4" s="4" t="s">
         <v>29</v>
       </c>
@@ -1340,14 +1773,14 @@
       <c r="L4" s="4"/>
     </row>
     <row r="5" spans="1:12" ht="100" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="5" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="3" t="s">
         <v>40</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -1374,14 +1807,14 @@
       <c r="L5" s="4"/>
     </row>
     <row r="6" spans="1:12" ht="100" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="5" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="3" t="s">
         <v>45</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -1390,10 +1823,10 @@
       <c r="F6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="3" t="s">
         <v>49</v>
       </c>
       <c r="I6" s="3" t="s">
@@ -1408,14 +1841,14 @@
       <c r="L6" s="4"/>
     </row>
     <row r="7" spans="1:12" ht="125" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="5" t="s">
+      <c r="A7" s="6"/>
+      <c r="B7" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="3" t="s">
         <v>52</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -1424,10 +1857,10 @@
       <c r="F7" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="3" t="s">
         <v>56</v>
       </c>
       <c r="I7" s="3" t="s">
@@ -1441,17 +1874,17 @@
       </c>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="1:12" ht="150" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="137.5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -1460,10 +1893,10 @@
       <c r="F8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="3" t="s">
         <v>63</v>
       </c>
       <c r="I8" s="3" t="s">
@@ -1478,13 +1911,13 @@
       <c r="L8" s="4"/>
     </row>
     <row r="9" spans="1:12" ht="100" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="3" t="s">
         <v>66</v>
       </c>
       <c r="E9" s="3" t="s">
@@ -1493,10 +1926,10 @@
       <c r="F9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="3" t="s">
         <v>69</v>
       </c>
       <c r="I9" s="3" t="s">
@@ -1509,30 +1942,228 @@
         <v>6</v>
       </c>
       <c r="L9" s="4"/>
+    </row>
+    <row r="10" spans="1:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="100" x14ac:dyDescent="0.25">
+      <c r="B11" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L11" s="4"/>
+    </row>
+    <row r="12" spans="1:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="162.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="125" x14ac:dyDescent="0.25">
+      <c r="B14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="137.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B16" s="4" t="s">
+        <v>106</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:A7"/>
   </mergeCells>
-  <conditionalFormatting sqref="I2:I9">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+  <conditionalFormatting sqref="I2:I15">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"Partial"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"Fail"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"Fail"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>"Partial"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I9" xr:uid="{BCFD4413-29E0-4AD9-9329-5E1A03AA9073}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I15" xr:uid="{BCFD4413-29E0-4AD9-9329-5E1A03AA9073}">
       <formula1>"Pass,Fail,Partial"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:K9" xr:uid="{801B61C1-78CF-412E-B767-F116E7C74FA1}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:K15" xr:uid="{801B61C1-78CF-412E-B767-F116E7C74FA1}">
       <formula1>"High,Medium, Low"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1741,6 +2372,156 @@
         <oleObject progId="Packager Shell Object" dvAspect="DVASPECT_ICON" shapeId="2063" r:id="rId18"/>
       </mc:Fallback>
     </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Packager Shell Object" dvAspect="DVASPECT_ICON" shapeId="2065" r:id="rId20">
+          <objectPr defaultSize="0" autoPict="0" r:id="rId21">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>228600</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>546100</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>730250</xdr:colOff>
+                <xdr:row>9</xdr:row>
+                <xdr:rowOff>1085850</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Packager Shell Object" dvAspect="DVASPECT_ICON" shapeId="2065" r:id="rId20"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Packager Shell Object" dvAspect="DVASPECT_ICON" shapeId="2067" r:id="rId22">
+          <objectPr defaultSize="0" autoPict="0" r:id="rId23">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>133350</xdr:colOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>425450</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>736600</xdr:colOff>
+                <xdr:row>10</xdr:row>
+                <xdr:rowOff>1047750</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Packager Shell Object" dvAspect="DVASPECT_ICON" shapeId="2067" r:id="rId22"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Packager Shell Object" dvAspect="DVASPECT_ICON" shapeId="2070" r:id="rId24">
+          <objectPr defaultSize="0" autoPict="0" r:id="rId25">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>184150</xdr:colOff>
+                <xdr:row>11</xdr:row>
+                <xdr:rowOff>349250</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>698500</xdr:colOff>
+                <xdr:row>11</xdr:row>
+                <xdr:rowOff>971550</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Packager Shell Object" dvAspect="DVASPECT_ICON" shapeId="2070" r:id="rId24"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Packager Shell Object" dvAspect="DVASPECT_ICON" shapeId="2073" r:id="rId26">
+          <objectPr defaultSize="0" autoPict="0" r:id="rId27">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>107950</xdr:colOff>
+                <xdr:row>12</xdr:row>
+                <xdr:rowOff>628650</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>723900</xdr:colOff>
+                <xdr:row>12</xdr:row>
+                <xdr:rowOff>1314450</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Packager Shell Object" dvAspect="DVASPECT_ICON" shapeId="2073" r:id="rId26"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Packager Shell Object" dvAspect="DVASPECT_ICON" shapeId="2076" r:id="rId28">
+          <objectPr defaultSize="0" autoPict="0" r:id="rId29">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>190500</xdr:colOff>
+                <xdr:row>13</xdr:row>
+                <xdr:rowOff>285750</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>717550</xdr:colOff>
+                <xdr:row>13</xdr:row>
+                <xdr:rowOff>863600</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Packager Shell Object" dvAspect="DVASPECT_ICON" shapeId="2076" r:id="rId28"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <oleObject progId="Packager Shell Object" dvAspect="DVASPECT_ICON" shapeId="2079" r:id="rId30">
+          <objectPr defaultSize="0" autoPict="0" r:id="rId31">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>88900</xdr:colOff>
+                <xdr:row>14</xdr:row>
+                <xdr:rowOff>508000</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>11</xdr:col>
+                <xdr:colOff>679450</xdr:colOff>
+                <xdr:row>14</xdr:row>
+                <xdr:rowOff>1193800</xdr:rowOff>
+              </to>
+            </anchor>
+          </objectPr>
+        </oleObject>
+      </mc:Choice>
+      <mc:Fallback>
+        <oleObject progId="Packager Shell Object" dvAspect="DVASPECT_ICON" shapeId="2079" r:id="rId30"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
   </oleObjects>
 </worksheet>
 </file>